--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.064238635052622</v>
+        <v>0.822938778196051</v>
       </c>
       <c r="D2" t="n">
-        <v>7.818619255970961</v>
+        <v>1.270525629095281</v>
       </c>
       <c r="E2" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F2" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.45579287122174</v>
+        <v>4.299066341573532</v>
       </c>
       <c r="D3" t="n">
-        <v>20.2433993200373</v>
+        <v>3.289552389506062</v>
       </c>
       <c r="E3" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F3" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.96778462848277</v>
+        <v>5.51976500212845</v>
       </c>
       <c r="D4" t="n">
-        <v>33.28996486626555</v>
+        <v>5.409619290768152</v>
       </c>
       <c r="E4" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F4" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.17613480391665</v>
+        <v>6.041121905636456</v>
       </c>
       <c r="D5" t="n">
-        <v>37.7733400416865</v>
+        <v>6.138167756774057</v>
       </c>
       <c r="E5" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F5" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.8189679115456</v>
+        <v>6.79558228562616</v>
       </c>
       <c r="D6" t="n">
-        <v>39.39935307555986</v>
+        <v>6.402394874778477</v>
       </c>
       <c r="E6" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F6" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.30979910974615</v>
+        <v>6.71284235533375</v>
       </c>
       <c r="D7" t="n">
-        <v>43.07688193345606</v>
+        <v>6.999993314186611</v>
       </c>
       <c r="E7" t="n">
-        <v>12.67281069919838</v>
+        <v>2.059331738619736</v>
       </c>
       <c r="F7" t="n">
-        <v>12.36513090534311</v>
+        <v>2.009333772118256</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
